--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -8490,7 +8490,7 @@
         <v>135905068</v>
       </c>
       <c r="B72" t="n">
-        <v>92688</v>
+        <v>92691</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>135905063</v>
       </c>
       <c r="B93" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135905051</v>
       </c>
       <c r="B98" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>135905055</v>
       </c>
       <c r="B99" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>135905062</v>
       </c>
       <c r="B100" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>135905065</v>
       </c>
       <c r="B101" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>135905061</v>
       </c>
       <c r="B295" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>135905064</v>
       </c>
       <c r="B296" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>135905071</v>
       </c>
       <c r="B297" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>135905072</v>
       </c>
       <c r="B298" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>135905073</v>
       </c>
       <c r="B299" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -8490,7 +8490,7 @@
         <v>135905068</v>
       </c>
       <c r="B72" t="n">
-        <v>92691</v>
+        <v>92692</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>135905063</v>
       </c>
       <c r="B93" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135905051</v>
       </c>
       <c r="B98" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>135905055</v>
       </c>
       <c r="B99" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>135905062</v>
       </c>
       <c r="B100" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>135905065</v>
       </c>
       <c r="B101" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>135905061</v>
       </c>
       <c r="B295" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>135905064</v>
       </c>
       <c r="B296" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>135905071</v>
       </c>
       <c r="B297" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>135905072</v>
       </c>
       <c r="B298" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>135905073</v>
       </c>
       <c r="B299" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -6232,7 +6232,7 @@
         <v>135905043</v>
       </c>
       <c r="B52" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>135905044</v>
       </c>
       <c r="B53" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>136573905</v>
       </c>
       <c r="B68" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>135905068</v>
       </c>
       <c r="B72" t="n">
-        <v>92692</v>
+        <v>92697</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>135905045</v>
       </c>
       <c r="B90" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>136573900</v>
       </c>
       <c r="B91" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>136573925</v>
       </c>
       <c r="B92" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>135905063</v>
       </c>
       <c r="B93" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>135905051</v>
       </c>
       <c r="B98" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>135905055</v>
       </c>
       <c r="B99" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>135905062</v>
       </c>
       <c r="B100" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>135905065</v>
       </c>
       <c r="B101" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>136573931</v>
       </c>
       <c r="B118" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>135905039</v>
       </c>
       <c r="B136" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>135905041</v>
       </c>
       <c r="B137" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>135905046</v>
       </c>
       <c r="B138" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>135905052</v>
       </c>
       <c r="B139" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>135905059</v>
       </c>
       <c r="B140" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>136573908</v>
       </c>
       <c r="B152" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>136573912</v>
       </c>
       <c r="B153" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>136573914</v>
       </c>
       <c r="B154" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>136573915</v>
       </c>
       <c r="B155" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>136573916</v>
       </c>
       <c r="B156" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>135905048</v>
       </c>
       <c r="B188" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>136573927</v>
       </c>
       <c r="B202" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>135905069</v>
       </c>
       <c r="B219" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>136573899</v>
       </c>
       <c r="B225" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>136573903</v>
       </c>
       <c r="B226" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>136573924</v>
       </c>
       <c r="B227" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>136573935</v>
       </c>
       <c r="B228" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>136573936</v>
       </c>
       <c r="B229" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>136573944</v>
       </c>
       <c r="B230" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>136573946</v>
       </c>
       <c r="B231" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>136573947</v>
       </c>
       <c r="B232" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26428,7 +26428,7 @@
         <v>135905057</v>
       </c>
       <c r="B236" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>135905038</v>
       </c>
       <c r="B240" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>136573922</v>
       </c>
       <c r="B241" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>136573930</v>
       </c>
       <c r="B242" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>136573934</v>
       </c>
       <c r="B243" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>135905042</v>
       </c>
       <c r="B245" t="n">
-        <v>41631</v>
+        <v>41633</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>135905061</v>
       </c>
       <c r="B295" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>135905064</v>
       </c>
       <c r="B296" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>135905071</v>
       </c>
       <c r="B297" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>135905072</v>
       </c>
       <c r="B298" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>135905073</v>
       </c>
       <c r="B299" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>135905040</v>
       </c>
       <c r="B334" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -37313,7 +37313,7 @@
         <v>135905047</v>
       </c>
       <c r="B335" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>135905053</v>
       </c>
       <c r="B336" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>135905054</v>
       </c>
       <c r="B337" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>135905056</v>
       </c>
       <c r="B338" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -37761,7 +37761,7 @@
         <v>135905058</v>
       </c>
       <c r="B339" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>135905066</v>
       </c>
       <c r="B340" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>135905067</v>
       </c>
       <c r="B341" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>136573902</v>
       </c>
       <c r="B358" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>136573904</v>
       </c>
       <c r="B359" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>136573907</v>
       </c>
       <c r="B360" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>136573909</v>
       </c>
       <c r="B361" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>136573911</v>
       </c>
       <c r="B362" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>136573913</v>
       </c>
       <c r="B363" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>136573917</v>
       </c>
       <c r="B364" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>136573948</v>
       </c>
       <c r="B365" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>135905049</v>
       </c>
       <c r="B373" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>136573929</v>
       </c>
       <c r="B375" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>136573933</v>
       </c>
       <c r="B376" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>136573905</v>
       </c>
       <c r="B68" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>136573900</v>
       </c>
       <c r="B91" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>136573925</v>
       </c>
       <c r="B92" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>136573931</v>
       </c>
       <c r="B118" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>136573908</v>
       </c>
       <c r="B152" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>136573912</v>
       </c>
       <c r="B153" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>136573914</v>
       </c>
       <c r="B154" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>136573915</v>
       </c>
       <c r="B155" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>136573916</v>
       </c>
       <c r="B156" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>136573927</v>
       </c>
       <c r="B202" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>136573899</v>
       </c>
       <c r="B225" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>136573903</v>
       </c>
       <c r="B226" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>136573924</v>
       </c>
       <c r="B227" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>136573935</v>
       </c>
       <c r="B228" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>136573936</v>
       </c>
       <c r="B229" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>136573944</v>
       </c>
       <c r="B230" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>136573946</v>
       </c>
       <c r="B231" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>136573947</v>
       </c>
       <c r="B232" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>136573902</v>
       </c>
       <c r="B358" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>136573904</v>
       </c>
       <c r="B359" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>136573907</v>
       </c>
       <c r="B360" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>136573909</v>
       </c>
       <c r="B361" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>136573911</v>
       </c>
       <c r="B362" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>136573913</v>
       </c>
       <c r="B363" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>136573917</v>
       </c>
       <c r="B364" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>136573948</v>
       </c>
       <c r="B365" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>136573929</v>
       </c>
       <c r="B375" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>136573933</v>
       </c>
       <c r="B376" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>136573905</v>
       </c>
       <c r="B68" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>136573900</v>
       </c>
       <c r="B91" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>136573925</v>
       </c>
       <c r="B92" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>136573931</v>
       </c>
       <c r="B118" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>136573908</v>
       </c>
       <c r="B152" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>136573912</v>
       </c>
       <c r="B153" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>136573914</v>
       </c>
       <c r="B154" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>136573915</v>
       </c>
       <c r="B155" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>136573916</v>
       </c>
       <c r="B156" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>136573927</v>
       </c>
       <c r="B202" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>136573899</v>
       </c>
       <c r="B225" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>136573903</v>
       </c>
       <c r="B226" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>136573924</v>
       </c>
       <c r="B227" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>136573935</v>
       </c>
       <c r="B228" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>136573936</v>
       </c>
       <c r="B229" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>136573944</v>
       </c>
       <c r="B230" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>136573946</v>
       </c>
       <c r="B231" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>136573947</v>
       </c>
       <c r="B232" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>136573902</v>
       </c>
       <c r="B358" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>136573904</v>
       </c>
       <c r="B359" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>136573907</v>
       </c>
       <c r="B360" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>136573909</v>
       </c>
       <c r="B361" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>136573911</v>
       </c>
       <c r="B362" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>136573913</v>
       </c>
       <c r="B363" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>136573917</v>
       </c>
       <c r="B364" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>136573948</v>
       </c>
       <c r="B365" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>136573929</v>
       </c>
       <c r="B375" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>136573933</v>
       </c>
       <c r="B376" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>136573905</v>
       </c>
       <c r="B68" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>136573900</v>
       </c>
       <c r="B91" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>136573925</v>
       </c>
       <c r="B92" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>136573931</v>
       </c>
       <c r="B118" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>136573908</v>
       </c>
       <c r="B152" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>136573912</v>
       </c>
       <c r="B153" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>136573914</v>
       </c>
       <c r="B154" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>136573915</v>
       </c>
       <c r="B155" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>136573916</v>
       </c>
       <c r="B156" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>136573927</v>
       </c>
       <c r="B202" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>136573899</v>
       </c>
       <c r="B225" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>136573903</v>
       </c>
       <c r="B226" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>136573924</v>
       </c>
       <c r="B227" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>136573935</v>
       </c>
       <c r="B228" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>136573936</v>
       </c>
       <c r="B229" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>136573944</v>
       </c>
       <c r="B230" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>136573946</v>
       </c>
       <c r="B231" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>136573947</v>
       </c>
       <c r="B232" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>136573902</v>
       </c>
       <c r="B358" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>136573904</v>
       </c>
       <c r="B359" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>136573907</v>
       </c>
       <c r="B360" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>136573909</v>
       </c>
       <c r="B361" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>136573911</v>
       </c>
       <c r="B362" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>136573913</v>
       </c>
       <c r="B363" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>136573917</v>
       </c>
       <c r="B364" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>136573948</v>
       </c>
       <c r="B365" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>136573929</v>
       </c>
       <c r="B375" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>136573933</v>
       </c>
       <c r="B376" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>136573905</v>
       </c>
       <c r="B68" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>136573900</v>
       </c>
       <c r="B91" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>136573925</v>
       </c>
       <c r="B92" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>136573931</v>
       </c>
       <c r="B118" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>136573908</v>
       </c>
       <c r="B152" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>136573912</v>
       </c>
       <c r="B153" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>136573914</v>
       </c>
       <c r="B154" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>136573915</v>
       </c>
       <c r="B155" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>136573916</v>
       </c>
       <c r="B156" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>136573927</v>
       </c>
       <c r="B202" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>136573899</v>
       </c>
       <c r="B225" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>136573903</v>
       </c>
       <c r="B226" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>136573924</v>
       </c>
       <c r="B227" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>136573935</v>
       </c>
       <c r="B228" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>136573936</v>
       </c>
       <c r="B229" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>136573944</v>
       </c>
       <c r="B230" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>136573946</v>
       </c>
       <c r="B231" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>136573947</v>
       </c>
       <c r="B232" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>136573902</v>
       </c>
       <c r="B358" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>136573904</v>
       </c>
       <c r="B359" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>136573907</v>
       </c>
       <c r="B360" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>136573909</v>
       </c>
       <c r="B361" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>136573911</v>
       </c>
       <c r="B362" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>136573913</v>
       </c>
       <c r="B363" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>136573917</v>
       </c>
       <c r="B364" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>136573948</v>
       </c>
       <c r="B365" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>136573929</v>
       </c>
       <c r="B375" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>136573933</v>
       </c>
       <c r="B376" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 31958-2026 artfynd.xlsx
+++ b/artfynd/A 31958-2026 artfynd.xlsx
@@ -7912,7 +7912,7 @@
         <v>135905612</v>
       </c>
       <c r="B67" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>136573905</v>
       </c>
       <c r="B68" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>136573919</v>
       </c>
       <c r="B77" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>136573900</v>
       </c>
       <c r="B91" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>136573925</v>
       </c>
       <c r="B92" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>136573920</v>
       </c>
       <c r="B94" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136573918</v>
       </c>
       <c r="B102" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>136573923</v>
       </c>
       <c r="B103" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>136573926</v>
       </c>
       <c r="B104" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>136573932</v>
       </c>
       <c r="B105" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>136573931</v>
       </c>
       <c r="B118" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>136573908</v>
       </c>
       <c r="B152" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>136573912</v>
       </c>
       <c r="B153" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>136573914</v>
       </c>
       <c r="B154" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>136573915</v>
       </c>
       <c r="B155" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>136573916</v>
       </c>
       <c r="B156" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>136573927</v>
       </c>
       <c r="B202" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>136573899</v>
       </c>
       <c r="B225" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>136573903</v>
       </c>
       <c r="B226" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>136573924</v>
       </c>
       <c r="B227" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>136573935</v>
       </c>
       <c r="B228" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>136573936</v>
       </c>
       <c r="B229" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>136573944</v>
       </c>
       <c r="B230" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>136573946</v>
       </c>
       <c r="B231" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>136573947</v>
       </c>
       <c r="B232" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>136573901</v>
       </c>
       <c r="B319" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         <v>136573906</v>
       </c>
       <c r="B320" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35746,7 +35746,7 @@
         <v>136573921</v>
       </c>
       <c r="B321" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35853,7 +35853,7 @@
         <v>136573937</v>
       </c>
       <c r="B322" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>136573938</v>
       </c>
       <c r="B323" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         <v>136573939</v>
       </c>
       <c r="B324" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>136573940</v>
       </c>
       <c r="B325" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>136573943</v>
       </c>
       <c r="B326" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>136573945</v>
       </c>
       <c r="B327" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>136573902</v>
       </c>
       <c r="B358" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>136573904</v>
       </c>
       <c r="B359" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>136573907</v>
       </c>
       <c r="B360" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>136573909</v>
       </c>
       <c r="B361" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>136573911</v>
       </c>
       <c r="B362" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>136573913</v>
       </c>
       <c r="B363" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>136573917</v>
       </c>
       <c r="B364" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>136573948</v>
       </c>
       <c r="B365" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -41705,7 +41705,7 @@
         <v>136573929</v>
       </c>
       <c r="B375" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>136573933</v>
       </c>
       <c r="B376" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
